--- a/output_plant/stomata_Intermediate_wang_2015.xlsx
+++ b/output_plant/stomata_Intermediate_wang_2015.xlsx
@@ -614,7 +614,7 @@
     <t xml:space="preserve">10.1371/journal.pone.0130941</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.ncei.noaa.gov/pub/data/paleo/climate_forcing/trace_gases/Paleo-pCO2/stomata-si_wang_2015.xlsx</t>
+    <t xml:space="preserve">stomata-si_wang_2015_p1.0.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">Harper and Giulivi</t>

--- a/output_plant/stomata_Intermediate_wang_2015.xlsx
+++ b/output_plant/stomata_Intermediate_wang_2015.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="210">
   <si>
     <t>eDab</t>
   </si>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">dustin.t.harper@utah.edu; claudiag@ldeo.columbia.edu</t>
   </si>
   <si>
-    <t xml:space="preserve">Stratigraphic study</t>
+    <t xml:space="preserve">Stratigraphic study; biostratigraphy updated to GTS2020</t>
   </si>
   <si>
     <t xml:space="preserve">Cuppressaceae / Metasequoia</t>
@@ -652,16 +652,6 @@
   </si>
   <si>
     <t xml:space="preserve">BQC001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SG001,
-SG002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">156u01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NR001</t>
   </si>
 </sst>
 </file>
@@ -2334,61 +2324,29 @@
       <c r="BK8" s="1"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>34.9833333333333</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>136.1</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>2.6</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="23"/>
       <c r="I9" s="23"/>
-      <c r="J9" s="23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
       <c r="P9" s="26"/>
       <c r="Q9" s="26"/>
-      <c r="R9"/>
       <c r="S9" s="24"/>
       <c r="T9" s="24"/>
-      <c r="U9"/>
       <c r="V9" s="26"/>
       <c r="W9" s="26"/>
-      <c r="X9"/>
       <c r="Y9" s="24"/>
       <c r="Z9" s="24"/>
-      <c r="AA9"/>
       <c r="AB9" s="24"/>
       <c r="AC9" s="24"/>
       <c r="AD9" s="1"/>
@@ -2397,7 +2355,6 @@
       <c r="AG9" s="1"/>
       <c r="AH9" s="25"/>
       <c r="AI9" s="25"/>
-      <c r="AJ9"/>
       <c r="AK9" s="1"/>
       <c r="AL9" s="1"/>
       <c r="AM9" s="1"/>
@@ -2427,61 +2384,29 @@
       <c r="BK9" s="1"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>37.1166666666667</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>138.8</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>1.85</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="23"/>
       <c r="I10" s="23"/>
-      <c r="J10" s="23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
       <c r="P10" s="26"/>
       <c r="Q10" s="26"/>
-      <c r="R10"/>
       <c r="S10" s="24"/>
       <c r="T10" s="24"/>
-      <c r="U10"/>
       <c r="V10" s="26"/>
       <c r="W10" s="26"/>
-      <c r="X10"/>
       <c r="Y10" s="24"/>
       <c r="Z10" s="24"/>
-      <c r="AA10"/>
       <c r="AB10" s="24"/>
       <c r="AC10" s="24"/>
       <c r="AD10" s="1"/>
@@ -2490,7 +2415,6 @@
       <c r="AG10" s="1"/>
       <c r="AH10" s="25"/>
       <c r="AI10" s="25"/>
-      <c r="AJ10"/>
       <c r="AK10" s="1"/>
       <c r="AL10" s="1"/>
       <c r="AM10" s="1"/>
@@ -2520,61 +2444,29 @@
       <c r="BK10" s="1"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>200</v>
-      </c>
-      <c r="F11" s="25" t="n">
-        <v>34.7333333333333</v>
-      </c>
-      <c r="G11" s="25" t="n">
-        <v>135.7</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="23"/>
       <c r="I11" s="23"/>
-      <c r="J11" s="23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>204</v>
-      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
       <c r="P11" s="26"/>
       <c r="Q11" s="26"/>
-      <c r="R11"/>
       <c r="S11" s="24"/>
       <c r="T11" s="24"/>
-      <c r="U11"/>
       <c r="V11" s="26"/>
       <c r="W11" s="26"/>
-      <c r="X11"/>
       <c r="Y11" s="24"/>
       <c r="Z11" s="24"/>
-      <c r="AA11"/>
       <c r="AB11" s="24"/>
       <c r="AC11" s="24"/>
       <c r="AD11" s="1"/>
@@ -2583,7 +2475,6 @@
       <c r="AG11" s="1"/>
       <c r="AH11" s="25"/>
       <c r="AI11" s="25"/>
-      <c r="AJ11"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
       <c r="AM11" s="1"/>
